--- a/outputs/daily/hr_rankings_2026-10-06.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-06.xlsx
@@ -1045,7 +1045,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>55.9</v>
+        <v>55.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot</t>
+          <t>Elite Power, Strong Barrel</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1091,7 +1091,7 @@
         <v>43.9</v>
       </c>
       <c r="S3" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -1101,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1855,56 +1851,56 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>669257</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fernando Tatis</t>
+          <t>Will Smith</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>54.2</v>
+        <v>54.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1918,62 +1914,58 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>57.9</v>
+        <v>51.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>46.2</v>
+        <v>24</v>
       </c>
       <c r="R6" t="n">
-        <v>22.6</v>
+        <v>43.9</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>74.2</v>
+        <v>100</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1998,129 +1990,137 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>53.27</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>93.02</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>104.4475</t>
+          <t>100.2559</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4964</t>
+          <t>0.5002</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.2079</t>
+          <t>0.2249</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3763</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>75.58</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>57.84</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>22.36</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1801</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.4132</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1122</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+          <t>26.46</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr"/>
@@ -2131,56 +2131,56 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>669257</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Will Smith</t>
+          <t>Fernando Tatis</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>53.9</v>
+        <v>54.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2194,26 +2194,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>51.1</v>
+        <v>57.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>24</v>
+        <v>46.2</v>
       </c>
       <c r="R7" t="n">
-        <v>43.9</v>
+        <v>22.6</v>
       </c>
       <c r="S7" t="n">
-        <v>90.40000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T7" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>100</v>
+        <v>74.2</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -2274,137 +2274,129 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>53.27</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>93.02</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>100.2559</t>
+          <t>104.4475</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.5002</t>
+          <t>0.4964</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.2249</t>
+          <t>0.2079</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3763</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>75.58</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>57.84</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.1801</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1122</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>26.46</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr"/>
@@ -3523,56 +3515,56 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>601713</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>49.8</v>
+        <v>50.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3586,62 +3578,58 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>47.1</v>
+        <v>45.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>48.2</v>
+        <v>24</v>
       </c>
       <c r="R12" t="n">
-        <v>22.6</v>
+        <v>43.9</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U12" t="n">
-        <v>13.3</v>
+        <v>48.3</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3661,134 +3649,142 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>EV profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>101.5782</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4427</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1878</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>40.24</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.3834</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.1122</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>34.35</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+          <t>26.46</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr"/>
@@ -3799,24 +3795,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>592518</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Manny Machado</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-07T01:30:00Z</t>
@@ -3829,17 +3825,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>601713</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3862,26 +3858,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>47.9</v>
+        <v>47.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>46.2</v>
+        <v>48.2</v>
       </c>
       <c r="R13" t="n">
         <v>22.6</v>
       </c>
       <c r="S13" t="n">
-        <v>92.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>41.7</v>
+        <v>13.3</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3895,7 +3891,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -3937,127 +3933,127 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>45.97</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>90.94</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>101.7846</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4425</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1911</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3358</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>74.64</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>77.51</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>28.71</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1885</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>40.24</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.4132</t>
+          <t>0.3834</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>25.43</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr"/>
@@ -4075,47 +4071,47 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>671739</t>
+          <t>592518</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Michael Harris II</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4124,7 +4120,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>48.7</v>
+        <v>49.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4138,58 +4134,62 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>45.1</v>
+        <v>47.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>26.6</v>
+        <v>46.2</v>
       </c>
       <c r="R14" t="n">
-        <v>43.9</v>
+        <v>22.6</v>
       </c>
       <c r="S14" t="n">
-        <v>86.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>32</v>
+        <v>41.7</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4209,27 +4209,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4239,112 +4239,104 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>46.34</t>
+          <t>45.97</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>90.41</t>
+          <t>90.94</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>103.0958</t>
+          <t>101.7846</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.4653</t>
+          <t>0.4425</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1816</t>
+          <t>0.1911</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3339</t>
+          <t>0.3358</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>74.72</t>
+          <t>74.64</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>44.79</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>28.71</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1859</t>
+          <t>0.1885</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>22.66</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr"/>
@@ -4355,47 +4347,47 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>671739</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>601713</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -4404,7 +4396,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>47</v>
+        <v>48.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4418,62 +4410,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>39.5</v>
+        <v>45.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>48.2</v>
+        <v>26.6</v>
       </c>
       <c r="R15" t="n">
-        <v>22.6</v>
+        <v>43.9</v>
       </c>
       <c r="S15" t="n">
-        <v>90.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>37.8</v>
+        <v>32</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4493,134 +4481,142 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>46.34</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>90.41</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>103.0958</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4653</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1816</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3339</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>74.72</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1859</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>40.24</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3834</t>
+          <t>0.3257</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>34.35</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>22.66</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr"/>
@@ -4631,12 +4627,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4661,7 +4657,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4680,7 +4676,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>46.1</v>
+        <v>47</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4694,11 +4690,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>38.2</v>
+        <v>39.5</v>
       </c>
       <c r="Q16" t="n">
         <v>48.2</v>
@@ -4707,13 +4703,13 @@
         <v>22.6</v>
       </c>
       <c r="S16" t="n">
-        <v>71.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>25.3</v>
+        <v>37.8</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -4727,7 +4723,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -4769,7 +4765,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
@@ -4784,12 +4780,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4799,67 +4795,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>73.16</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -4907,56 +4903,56 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>601713</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>45.2</v>
+        <v>46.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4970,26 +4966,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>45.7</v>
+        <v>38.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>24</v>
+        <v>48.2</v>
       </c>
       <c r="R17" t="n">
-        <v>43.9</v>
+        <v>22.6</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T17" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>48.3</v>
+        <v>25.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -5003,7 +4999,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -5045,12 +5041,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -5060,127 +5056,119 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>101.5782</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1878</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>73.16</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>40.24</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.3834</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1122</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>26.46</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
+          <t>34.35</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr"/>
@@ -5191,24 +5179,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>663586</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-06T22:00:00Z</t>
@@ -5221,26 +5209,26 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>45</v>
+        <v>44.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5254,62 +5242,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>32.7</v>
+        <v>53.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>24</v>
+        <v>26.6</v>
       </c>
       <c r="R18" t="n">
         <v>43.9</v>
       </c>
       <c r="S18" t="n">
-        <v>95.5</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>29.2</v>
+        <v>48.7</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5334,22 +5318,22 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5359,97 +5343,97 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>13.24</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>98.5265</t>
+          <t>102.7231</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.4188</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1567</t>
+          <t>0.1956</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.3083</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>75.83</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>59.43</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>30.87</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1519</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.3257</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1122</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>22.66</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
@@ -5475,24 +5459,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>663586</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>2026-10-06T22:00:00Z</t>
@@ -5505,26 +5489,26 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5538,26 +5522,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>53.3</v>
+        <v>32.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>26.6</v>
+        <v>24</v>
       </c>
       <c r="R19" t="n">
         <v>43.9</v>
       </c>
       <c r="S19" t="n">
-        <v>52.4</v>
+        <v>93.2</v>
       </c>
       <c r="T19" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U19" t="n">
-        <v>48.7</v>
+        <v>29.2</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -5571,7 +5555,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -5614,22 +5598,22 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5639,97 +5623,97 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>13.24</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>102.7231</t>
+          <t>98.5265</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.4188</t>
+          <t>0.4311</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.1956</t>
+          <t>0.1567</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3083</t>
+          <t>0.3363</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>75.83</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>59.43</t>
+          <t>8.53</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>30.87</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1519</t>
+          <t>0.1823</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1122</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
@@ -5755,56 +5739,56 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>664034</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ty France</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>44.1</v>
+        <v>44.5</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -5818,62 +5802,58 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>40.6</v>
+        <v>39.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>46.2</v>
+        <v>24</v>
       </c>
       <c r="R20" t="n">
-        <v>22.6</v>
+        <v>43.9</v>
       </c>
       <c r="S20" t="n">
-        <v>81.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T20" t="n">
         <v>50</v>
       </c>
       <c r="U20" t="n">
-        <v>5.1</v>
+        <v>13</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5893,12 +5873,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -5908,12 +5888,12 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 6/29, 0 HR</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -5923,104 +5903,112 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>8.68</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>46.44</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>100.8422</t>
+          <t>100.1411</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.4222</t>
+          <t>0.4642</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.1709</t>
+          <t>0.1811</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.3273</t>
+          <t>0.3591</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.1758</t>
+          <t>0.1615</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>0.4132</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1122</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="BG20" t="inlineStr"/>
-      <c r="BH20" t="inlineStr"/>
+          <t>26.46</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr"/>
@@ -6031,32 +6019,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>691777</t>
+          <t>664034</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Ty France</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6066,21 +6054,21 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>43.7</v>
+        <v>44.1</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6094,26 +6082,26 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>35.1</v>
+        <v>40.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>24</v>
+        <v>46.2</v>
       </c>
       <c r="R21" t="n">
-        <v>43.9</v>
+        <v>22.6</v>
       </c>
       <c r="S21" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U21" t="n">
-        <v>26.1</v>
+        <v>5.1</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -6169,12 +6157,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -6184,12 +6172,12 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/17, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -6199,112 +6187,104 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>8.68</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>40.17</t>
+          <t>46.44</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>100.9708</t>
+          <t>100.8422</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.3621</t>
+          <t>0.4222</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.1493</t>
+          <t>0.1709</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3273</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>19.53</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>43.52</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>22.51</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.1594</t>
+          <t>0.1758</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.1122</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>26.46</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr"/>
+      <c r="BH21" t="inlineStr"/>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr"/>
@@ -6315,12 +6295,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -6345,7 +6325,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -6364,7 +6344,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>43.4</v>
+        <v>43.7</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -6378,11 +6358,11 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>39.3</v>
+        <v>36.4</v>
       </c>
       <c r="Q22" t="n">
         <v>24</v>
@@ -6391,49 +6371,45 @@
         <v>43.9</v>
       </c>
       <c r="S22" t="n">
-        <v>92.09999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="T22" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U22" t="n">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6458,22 +6434,22 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -6483,67 +6459,67 @@
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>88.81</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>100.1411</t>
+          <t>99.6965</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.4642</t>
+          <t>0.4378</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>0.1811</t>
+          <t>0.1686</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.3349</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>72.85</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>38.53</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>0.1615</t>
+          <t>0.1925</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
@@ -6599,56 +6575,56 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>593428</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Xander Bogaerts</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>41.4</v>
+        <v>41.1</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6662,26 +6638,26 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>36.4</v>
+        <v>28.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>24</v>
+        <v>46.2</v>
       </c>
       <c r="R23" t="n">
-        <v>43.9</v>
+        <v>22.6</v>
       </c>
       <c r="S23" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T23" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U23" t="n">
-        <v>66</v>
+        <v>52.8</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -6695,7 +6671,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -6737,27 +6713,27 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 7/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -6767,112 +6743,104 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>88.81</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>99.6965</t>
+          <t>100.2761</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.4378</t>
+          <t>0.3871</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>0.1686</t>
+          <t>0.1327</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>0.3349</t>
+          <t>0.3256</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>72.85</t>
+          <t>72.24</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>27.66</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>43.52</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>23.27</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>0.1925</t>
+          <t>0.1175</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>0.1122</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>26.46</t>
-        </is>
-      </c>
-      <c r="BG23" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH23" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr"/>
+      <c r="BH23" t="inlineStr"/>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr"/>
@@ -6883,12 +6851,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>593428</t>
+          <t>806956</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Xander Bogaerts</t>
+          <t>Ethan Salas</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -6913,7 +6881,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -6932,7 +6900,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>41.1</v>
+        <v>39.5</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -6946,11 +6914,11 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>28.7</v>
+        <v>22.6</v>
       </c>
       <c r="Q24" t="n">
         <v>46.2</v>
@@ -6959,13 +6927,13 @@
         <v>22.6</v>
       </c>
       <c r="S24" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T24" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U24" t="n">
-        <v>52.8</v>
+        <v>40.3</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -6979,7 +6947,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -7004,7 +6972,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr"/>
@@ -7026,92 +6994,92 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Contact streak: 7/20 over last 7 games</t>
+          <t>Contact streak: 7/18 over last 7 games</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>100.2761</t>
+          <t>98.8542</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>0.3871</t>
+          <t>0.316</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>0.1327</t>
+          <t>0.129</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>0.3256</t>
+          <t>0.227</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>72.24</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>43.52</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>23.27</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>0.1175</t>
+          <t>0.206</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
@@ -7159,32 +7127,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>806956</t>
+          <t>669221</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ethan Salas</t>
+          <t>Sean Murphy</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -7194,12 +7162,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -7208,7 +7176,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>39.5</v>
+        <v>37.9</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -7222,65 +7190,61 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>22.6</v>
+        <v>34</v>
       </c>
       <c r="Q25" t="n">
-        <v>46.2</v>
+        <v>26.6</v>
       </c>
       <c r="R25" t="n">
-        <v>22.6</v>
+        <v>43.9</v>
       </c>
       <c r="S25" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T25" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U25" t="n">
-        <v>40.3</v>
+        <v>3.4</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr"/>
@@ -7297,12 +7261,12 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -7312,119 +7276,127 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Contact streak: 7/18 over last 7 games</t>
+          <t>Last 7 games: 3/21, 0 HR</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>88.19</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>98.8542</t>
+          <t>101.2803</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>0.3548</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>0.2853</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>29.59</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>25.37</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>0.1456</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>0.4132</t>
+          <t>0.3257</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="BG25" t="inlineStr"/>
-      <c r="BH25" t="inlineStr"/>
+          <t>22.66</t>
+        </is>
+      </c>
+      <c r="BG25" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr"/>
@@ -7435,12 +7407,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>571771</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Enrique Hernández</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -7465,7 +7437,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -7484,7 +7456,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>38.7</v>
+        <v>37.8</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7498,11 +7470,11 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>33.9</v>
+        <v>32.6</v>
       </c>
       <c r="Q26" t="n">
         <v>24</v>
@@ -7511,49 +7483,45 @@
         <v>43.9</v>
       </c>
       <c r="S26" t="n">
-        <v>71.7</v>
+        <v>44.8</v>
       </c>
       <c r="T26" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U26" t="n">
-        <v>12</v>
+        <v>28.5</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7573,27 +7541,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 3/16, 1 HR</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
@@ -7603,67 +7571,67 @@
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>39.49</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>98.7109</t>
+          <t>99.9102</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.3751</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>0.1598</t>
+          <t>0.1548</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>0.3433</t>
+          <t>0.2814</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>70.82</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>14.73</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>42.96</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>25.54</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>0.1658</t>
+          <t>0.1735</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
@@ -7719,12 +7687,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>669221</t>
+          <t>645277</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sean Murphy</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -7749,7 +7717,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -7768,7 +7736,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>37.9</v>
+        <v>37.6</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -7782,26 +7750,26 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>34</v>
+        <v>15.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>26.6</v>
+        <v>24.6</v>
       </c>
       <c r="R27" t="n">
         <v>43.9</v>
       </c>
       <c r="S27" t="n">
-        <v>64.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U27" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -7815,7 +7783,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -7858,7 +7826,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -7868,12 +7836,12 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 0 HR</t>
+          <t>Last 7 games: 3/25, 0 HR</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
@@ -7883,67 +7851,67 @@
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>88.19</t>
+          <t>87.22</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>101.2803</t>
+          <t>96.687</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>0.3548</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1184</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>0.2853</t>
+          <t>0.2808</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>68.86</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>25.37</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>0.1456</t>
+          <t>0.146</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
@@ -7999,47 +7967,47 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>645277</t>
+          <t>687957</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Dustin Harris</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -8048,7 +8016,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>37.6</v>
+        <v>37.3</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -8062,58 +8030,62 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>15.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>24.6</v>
+        <v>46.2</v>
       </c>
       <c r="R28" t="n">
-        <v>43.9</v>
+        <v>22.6</v>
       </c>
       <c r="S28" t="n">
-        <v>94.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T28" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>16.6</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC28" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8133,12 +8105,12 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -8148,12 +8120,12 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/25, 0 HR</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
@@ -8163,112 +8135,104 @@
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>21.42</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>87.22</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>96.687</t>
+          <t>95.2049</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.3345</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>0.1184</t>
+          <t>0.0841</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>0.2808</t>
+          <t>0.2891</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>68.86</t>
+          <t>66.89</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>31.48</t>
+          <t>21.42</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.108</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>22.66</t>
-        </is>
-      </c>
-      <c r="BG28" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH28" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG28" t="inlineStr"/>
+      <c r="BH28" t="inlineStr"/>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr"/>
@@ -8279,56 +8243,56 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>687957</t>
+          <t>500743</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dustin Harris</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>37.3</v>
+        <v>36.4</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -8342,62 +8306,58 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>4.2</v>
+        <v>17.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>46.2</v>
+        <v>24</v>
       </c>
       <c r="R29" t="n">
-        <v>22.6</v>
+        <v>43.9</v>
       </c>
       <c r="S29" t="n">
-        <v>95.5</v>
+        <v>76.2</v>
       </c>
       <c r="T29" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U29" t="n">
-        <v>16.6</v>
+        <v>14.1</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8417,12 +8377,12 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -8432,12 +8392,12 @@
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 3/14, 0 HR</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
@@ -8447,104 +8407,112 @@
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>21.42</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>95.2049</t>
+          <t>98.0168</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>0.3345</t>
+          <t>0.3776</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>0.0841</t>
+          <t>0.1083</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>0.2891</t>
+          <t>0.3039</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>66.89</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>21.42</t>
+          <t>23.17</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>0.1273</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>0.4132</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1122</t>
         </is>
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="BG29" t="inlineStr"/>
-      <c r="BH29" t="inlineStr"/>
+          <t>26.46</t>
+        </is>
+      </c>
+      <c r="BG29" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr"/>
@@ -8555,56 +8523,56 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>630105</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jake Cronenworth</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>35.6</v>
+        <v>36</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -8618,62 +8586,58 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>16.4</v>
+        <v>33.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>46.2</v>
+        <v>24</v>
       </c>
       <c r="R30" t="n">
-        <v>22.6</v>
+        <v>43.9</v>
       </c>
       <c r="S30" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T30" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U30" t="n">
-        <v>57.8</v>
+        <v>12</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8693,27 +8657,27 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -8723,104 +8687,112 @@
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>32.49</t>
+          <t>37.53</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>87.59</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>97.7612</t>
+          <t>98.7109</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>0.3215</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>0.1042</t>
+          <t>0.1598</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>0.2882</t>
+          <t>0.3433</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>71.25</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>31.96</t>
+          <t>42.96</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>24.61</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>0.1065</t>
+          <t>0.1658</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>0.4132</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1122</t>
         </is>
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="BG30" t="inlineStr"/>
-      <c r="BH30" t="inlineStr"/>
+          <t>26.46</t>
+        </is>
+      </c>
+      <c r="BG30" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr"/>
@@ -8831,32 +8803,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>669242</t>
+          <t>630105</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Jake Cronenworth</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -8866,21 +8838,21 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>34.2</v>
+        <v>35.6</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -8898,22 +8870,22 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>20.2</v>
+        <v>16.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>22.9</v>
+        <v>46.2</v>
       </c>
       <c r="R31" t="n">
-        <v>43.9</v>
+        <v>22.6</v>
       </c>
       <c r="S31" t="n">
         <v>40.2</v>
       </c>
       <c r="T31" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U31" t="n">
-        <v>60.7</v>
+        <v>57.8</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -8969,12 +8941,12 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -8989,7 +8961,7 @@
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -8999,112 +8971,104 @@
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>34.37</t>
+          <t>32.49</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.59</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>98.7457</t>
+          <t>97.7612</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>0.3662</t>
+          <t>0.3215</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>0.3084</t>
+          <t>0.2882</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>71.25</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>31.96</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>24.61</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>0.1437</t>
+          <t>0.1065</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
-          <t>0.1122</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>26.46</t>
-        </is>
-      </c>
-      <c r="BG31" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH31" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG31" t="inlineStr"/>
+      <c r="BH31" t="inlineStr"/>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr"/>
@@ -11415,7 +11379,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -11434,7 +11398,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>55.9</v>
+        <v>55.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -11448,7 +11412,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot</t>
+          <t>Elite Power, Strong Barrel</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -11461,7 +11425,7 @@
         <v>43.9</v>
       </c>
       <c r="S3" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -11471,39 +11435,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12225,56 +12185,56 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>669257</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fernando Tatis</t>
+          <t>Will Smith</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>54.2</v>
+        <v>54.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -12288,62 +12248,58 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>57.9</v>
+        <v>51.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>46.2</v>
+        <v>24</v>
       </c>
       <c r="R6" t="n">
-        <v>22.6</v>
+        <v>43.9</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>74.2</v>
+        <v>100</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12368,129 +12324,137 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>53.27</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>93.02</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>104.4475</t>
+          <t>100.2559</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4964</t>
+          <t>0.5002</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.2079</t>
+          <t>0.2249</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3763</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>75.58</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>57.84</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>22.36</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1801</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.4132</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1122</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+          <t>26.46</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr"/>
@@ -12501,56 +12465,56 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>669257</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Will Smith</t>
+          <t>Fernando Tatis</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>53.9</v>
+        <v>54.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -12564,26 +12528,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>51.1</v>
+        <v>57.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>24</v>
+        <v>46.2</v>
       </c>
       <c r="R7" t="n">
-        <v>43.9</v>
+        <v>22.6</v>
       </c>
       <c r="S7" t="n">
-        <v>90.40000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T7" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>100</v>
+        <v>74.2</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -12597,7 +12561,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -12644,137 +12608,129 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>53.27</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>93.02</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>100.2559</t>
+          <t>104.4475</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.5002</t>
+          <t>0.4964</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.2249</t>
+          <t>0.2079</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3763</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>75.58</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>57.84</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.1801</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1122</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>26.46</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr"/>
@@ -13893,56 +13849,56 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>601713</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>49.8</v>
+        <v>50.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -13956,62 +13912,58 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>47.1</v>
+        <v>45.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>48.2</v>
+        <v>24</v>
       </c>
       <c r="R12" t="n">
-        <v>22.6</v>
+        <v>43.9</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U12" t="n">
-        <v>13.3</v>
+        <v>48.3</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14031,134 +13983,142 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>EV profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>101.5782</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4427</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1878</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>40.24</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.3834</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.1122</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>34.35</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+          <t>26.46</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr"/>
@@ -14169,24 +14129,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>592518</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Manny Machado</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-07T01:30:00Z</t>
@@ -14199,17 +14159,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>601713</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -14232,26 +14192,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>47.9</v>
+        <v>47.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>46.2</v>
+        <v>48.2</v>
       </c>
       <c r="R13" t="n">
         <v>22.6</v>
       </c>
       <c r="S13" t="n">
-        <v>92.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>41.7</v>
+        <v>13.3</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -14265,7 +14225,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -14307,127 +14267,127 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>45.97</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>90.94</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>101.7846</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4425</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1911</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3358</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>74.64</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>77.51</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>28.71</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1885</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>40.24</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.4132</t>
+          <t>0.3834</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>25.43</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr"/>
@@ -14445,47 +14405,47 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>671739</t>
+          <t>592518</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Michael Harris II</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -14494,7 +14454,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>48.7</v>
+        <v>49.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -14508,58 +14468,62 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>45.1</v>
+        <v>47.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>26.6</v>
+        <v>46.2</v>
       </c>
       <c r="R14" t="n">
-        <v>43.9</v>
+        <v>22.6</v>
       </c>
       <c r="S14" t="n">
-        <v>86.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>32</v>
+        <v>41.7</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14579,27 +14543,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -14609,112 +14573,104 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>46.34</t>
+          <t>45.97</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>90.41</t>
+          <t>90.94</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>103.0958</t>
+          <t>101.7846</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.4653</t>
+          <t>0.4425</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1816</t>
+          <t>0.1911</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3339</t>
+          <t>0.3358</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>74.72</t>
+          <t>74.64</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>44.79</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>28.71</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1859</t>
+          <t>0.1885</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>22.66</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr"/>
@@ -14725,47 +14681,47 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>671739</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>601713</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -14774,7 +14730,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>47</v>
+        <v>48.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -14788,62 +14744,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>39.5</v>
+        <v>45.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>48.2</v>
+        <v>26.6</v>
       </c>
       <c r="R15" t="n">
-        <v>22.6</v>
+        <v>43.9</v>
       </c>
       <c r="S15" t="n">
-        <v>90.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>37.8</v>
+        <v>32</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14863,134 +14815,142 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>46.34</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>90.41</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>103.0958</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4653</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1816</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3339</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>74.72</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1859</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>40.24</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3834</t>
+          <t>0.3257</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>34.35</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>22.66</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr"/>
@@ -15001,12 +14961,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -15031,7 +14991,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -15050,7 +15010,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>46.1</v>
+        <v>47</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -15064,11 +15024,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>38.2</v>
+        <v>39.5</v>
       </c>
       <c r="Q16" t="n">
         <v>48.2</v>
@@ -15077,13 +15037,13 @@
         <v>22.6</v>
       </c>
       <c r="S16" t="n">
-        <v>71.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>25.3</v>
+        <v>37.8</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -15097,7 +15057,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -15139,7 +15099,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
@@ -15154,12 +15114,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -15169,67 +15129,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>73.16</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -15277,56 +15237,56 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>601713</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>45.2</v>
+        <v>46.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -15340,26 +15300,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>45.7</v>
+        <v>38.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>24</v>
+        <v>48.2</v>
       </c>
       <c r="R17" t="n">
-        <v>43.9</v>
+        <v>22.6</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T17" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>48.3</v>
+        <v>25.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -15373,7 +15333,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -15415,12 +15375,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -15430,127 +15390,119 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>101.5782</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1878</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>73.16</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>40.24</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.3834</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1122</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>26.46</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
+          <t>34.35</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr"/>
@@ -15561,24 +15513,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>663586</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-06T22:00:00Z</t>
@@ -15591,26 +15543,26 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>45</v>
+        <v>44.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -15624,62 +15576,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>32.7</v>
+        <v>53.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>24</v>
+        <v>26.6</v>
       </c>
       <c r="R18" t="n">
         <v>43.9</v>
       </c>
       <c r="S18" t="n">
-        <v>95.5</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>29.2</v>
+        <v>48.7</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -15704,22 +15652,22 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -15729,97 +15677,97 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>13.24</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>98.5265</t>
+          <t>102.7231</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.4188</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1567</t>
+          <t>0.1956</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.3083</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>75.83</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>59.43</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>30.87</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1519</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.3257</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1122</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>22.66</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
@@ -15845,24 +15793,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>663586</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>2026-10-06T22:00:00Z</t>
@@ -15875,26 +15823,26 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -15908,26 +15856,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>53.3</v>
+        <v>32.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>26.6</v>
+        <v>24</v>
       </c>
       <c r="R19" t="n">
         <v>43.9</v>
       </c>
       <c r="S19" t="n">
-        <v>52.4</v>
+        <v>93.2</v>
       </c>
       <c r="T19" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U19" t="n">
-        <v>48.7</v>
+        <v>29.2</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -15941,7 +15889,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -15984,22 +15932,22 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -16009,97 +15957,97 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>13.24</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>102.7231</t>
+          <t>98.5265</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.4188</t>
+          <t>0.4311</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.1956</t>
+          <t>0.1567</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3083</t>
+          <t>0.3363</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>75.83</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>59.43</t>
+          <t>8.53</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>30.87</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1519</t>
+          <t>0.1823</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1122</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
@@ -16125,56 +16073,56 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>664034</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ty France</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>44.1</v>
+        <v>44.5</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -16188,62 +16136,58 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>40.6</v>
+        <v>39.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>46.2</v>
+        <v>24</v>
       </c>
       <c r="R20" t="n">
-        <v>22.6</v>
+        <v>43.9</v>
       </c>
       <c r="S20" t="n">
-        <v>81.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T20" t="n">
         <v>50</v>
       </c>
       <c r="U20" t="n">
-        <v>5.1</v>
+        <v>13</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -16263,12 +16207,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -16278,12 +16222,12 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 6/29, 0 HR</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -16293,104 +16237,112 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>8.68</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>46.44</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>100.8422</t>
+          <t>100.1411</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.4222</t>
+          <t>0.4642</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.1709</t>
+          <t>0.1811</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.3273</t>
+          <t>0.3591</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.1758</t>
+          <t>0.1615</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>0.4132</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1122</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="BG20" t="inlineStr"/>
-      <c r="BH20" t="inlineStr"/>
+          <t>26.46</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr"/>
@@ -16401,32 +16353,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>691777</t>
+          <t>664034</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Ty France</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -16436,21 +16388,21 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>43.7</v>
+        <v>44.1</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -16464,26 +16416,26 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>35.1</v>
+        <v>40.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>24</v>
+        <v>46.2</v>
       </c>
       <c r="R21" t="n">
-        <v>43.9</v>
+        <v>22.6</v>
       </c>
       <c r="S21" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U21" t="n">
-        <v>26.1</v>
+        <v>5.1</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -16539,12 +16491,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -16554,12 +16506,12 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/17, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -16569,112 +16521,104 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>8.68</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>40.17</t>
+          <t>46.44</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>100.9708</t>
+          <t>100.8422</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.3621</t>
+          <t>0.4222</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.1493</t>
+          <t>0.1709</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3273</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>19.53</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>43.52</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>22.51</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.1594</t>
+          <t>0.1758</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.1122</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>26.46</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr"/>
+      <c r="BH21" t="inlineStr"/>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr"/>

--- a/outputs/daily/hr_rankings_2026-10-06.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-06.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>58.2</v>
+        <v>59.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -811,7 +811,7 @@
         <v>40.1</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1044,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1068,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>58.1</v>
+        <v>57.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1092,7 +1088,7 @@
         <v>26.6</v>
       </c>
       <c r="R3" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S3" t="n">
         <v>96.59999999999999</v>
@@ -1283,7 +1279,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1579,27 +1575,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>660271</t>
+          <t>701538</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Shohei Ohtani</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1609,26 +1605,26 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>57.2</v>
+        <v>57</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1642,26 +1638,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>79.3</v>
+        <v>54.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>24</v>
+        <v>46.2</v>
       </c>
       <c r="R5" t="n">
-        <v>54.9</v>
+        <v>40.1</v>
       </c>
       <c r="S5" t="n">
-        <v>86.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>8.800000000000001</v>
+        <v>16.6</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1675,7 +1671,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1713,12 +1709,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1728,127 +1724,127 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/28, 0 HR</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>54.08</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>93.78</t>
+          <t>90.96</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>104.473</t>
+          <t>101.2045</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.5811</t>
+          <t>0.4907</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.2987</t>
+          <t>0.2228</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4054</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>75.03</t>
+          <t>72.95</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>52.94</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>31.92</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.2679</t>
+          <t>0.1881</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.1122</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>25.43</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr"/>
@@ -1859,56 +1855,56 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>701538</t>
+          <t>660271</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Shohei Ohtani</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>57</v>
+        <v>56.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1922,26 +1918,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>54.2</v>
+        <v>79.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>46.2</v>
+        <v>24</v>
       </c>
       <c r="R6" t="n">
-        <v>40.1</v>
+        <v>51.9</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>16.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1955,7 +1951,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1993,12 +1989,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2008,127 +2004,127 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 5/28, 0 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>18.53</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>54.08</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>90.96</t>
+          <t>93.78</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>101.2045</t>
+          <t>104.473</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4907</t>
+          <t>0.5811</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.2228</t>
+          <t>0.2987</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.4054</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>72.95</t>
+          <t>75.03</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>31.92</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1881</t>
+          <t>0.2679</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.4132</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1122</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>25.43</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr"/>
@@ -2164,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2188,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>56.3</v>
+        <v>55.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2212,7 +2208,7 @@
         <v>26.6</v>
       </c>
       <c r="R7" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S7" t="n">
         <v>93.2</v>
@@ -2403,7 +2399,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2444,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2468,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>56.2</v>
+        <v>55.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2492,7 +2488,7 @@
         <v>24</v>
       </c>
       <c r="R8" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S8" t="n">
         <v>94.90000000000001</v>
@@ -2683,7 +2679,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2699,27 +2695,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>660670</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ronald Acuña Jr.</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2729,17 +2725,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>601713</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2748,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>55.2</v>
+        <v>54.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2766,22 +2762,22 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>58.7</v>
+        <v>50.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>26.6</v>
+        <v>48.2</v>
       </c>
       <c r="R9" t="n">
-        <v>54.9</v>
+        <v>40.1</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>53.3</v>
+        <v>63.3</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -2795,7 +2791,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2833,142 +2829,142 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.53</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>102.9585</t>
+          <t>101.9338</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.507</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.2461</t>
+          <t>0.2007</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3753</t>
+          <t>0.3329</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>75.91</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>61.27</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>36.58</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.2056</t>
+          <t>0.1951</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>40.24</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.3834</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr"/>
@@ -2979,47 +2975,47 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>660670</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Ronald Acuña Jr.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>601713</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -3028,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>54.2</v>
+        <v>54.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3042,62 +3038,58 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>50.1</v>
+        <v>58.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>48.2</v>
+        <v>26.6</v>
       </c>
       <c r="R10" t="n">
-        <v>40.1</v>
+        <v>51.9</v>
       </c>
       <c r="S10" t="n">
-        <v>88.7</v>
+        <v>100</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>63.3</v>
+        <v>53.3</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3117,142 +3109,142 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>13.81</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>90.53</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.9338</t>
+          <t>102.9585</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.507</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.2461</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.3753</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>75.91</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>61.27</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>36.58</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1951</t>
+          <t>0.2056</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>40.24</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.3834</t>
+          <t>0.3257</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>22.66</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr"/>
@@ -3293,7 +3285,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3312,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>53.5</v>
+        <v>53.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3326,7 +3318,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3339,7 +3331,7 @@
         <v>40.1</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
@@ -3349,39 +3341,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3827,56 +3815,56 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>601713</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>52.4</v>
+        <v>51.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3890,62 +3878,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>47.1</v>
+        <v>45.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>48.2</v>
+        <v>24</v>
       </c>
       <c r="R13" t="n">
-        <v>40.1</v>
+        <v>51.9</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>13.3</v>
+        <v>48.3</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3965,142 +3949,142 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>EV profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>101.5782</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4427</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1878</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>40.24</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.3834</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.1122</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr"/>
@@ -4111,27 +4095,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Teoscar Hernández</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4141,26 +4125,26 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>601713</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>52</v>
+        <v>51.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4174,26 +4158,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>45.7</v>
+        <v>47.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>24</v>
+        <v>48.2</v>
       </c>
       <c r="R14" t="n">
-        <v>54.9</v>
+        <v>40.1</v>
       </c>
       <c r="S14" t="n">
-        <v>96.59999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>48.3</v>
+        <v>13.3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -4207,7 +4191,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -4245,142 +4229,142 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>101.5782</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1878</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>77.51</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>40.24</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.3834</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1122</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr"/>
@@ -4391,27 +4375,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>671739</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Michael Harris II</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4426,12 +4410,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>601713</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -4440,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>50.4</v>
+        <v>50.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4458,13 +4442,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>45.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>26.6</v>
+        <v>48.2</v>
       </c>
       <c r="R15" t="n">
-        <v>54.9</v>
+        <v>40.1</v>
       </c>
       <c r="S15" t="n">
         <v>86.40000000000001</v>
@@ -4473,7 +4457,7 @@
         <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>32</v>
+        <v>25.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -4525,142 +4509,142 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>46.34</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>90.41</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>103.0958</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.4653</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1816</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3339</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>74.72</t>
+          <t>73.16</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1859</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>40.24</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.3834</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr"/>
@@ -4701,7 +4685,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4720,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>49.7</v>
+        <v>50.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4734,7 +4718,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -4747,7 +4731,7 @@
         <v>40.1</v>
       </c>
       <c r="S16" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T16" t="n">
         <v>50</v>
@@ -4757,39 +4741,35 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4955,47 +4935,47 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>671739</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>601713</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -5004,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>48.7</v>
+        <v>49.9</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5018,62 +4998,58 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>38.2</v>
+        <v>45.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>48.2</v>
+        <v>26.6</v>
       </c>
       <c r="R17" t="n">
-        <v>40.1</v>
+        <v>51.9</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>25.3</v>
+        <v>32</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5093,142 +5069,142 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>46.34</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.41</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>103.0958</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4653</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1816</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3339</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>73.16</t>
+          <t>74.72</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1859</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>40.24</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.3834</t>
+          <t>0.3257</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>22.66</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr"/>
@@ -5824,7 +5800,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -5848,7 +5824,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>46.5</v>
+        <v>46</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -5872,7 +5848,7 @@
         <v>26.6</v>
       </c>
       <c r="R20" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S20" t="n">
         <v>52.4</v>
@@ -6063,7 +6039,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -6104,7 +6080,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6128,7 +6104,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>46.3</v>
+        <v>45.9</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6152,7 +6128,7 @@
         <v>24</v>
       </c>
       <c r="R21" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S21" t="n">
         <v>93.2</v>
@@ -6343,7 +6319,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -6359,27 +6335,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>806956</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Ethan Salas</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -6389,26 +6365,26 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>46.1</v>
+        <v>45.9</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -6422,26 +6398,26 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>39.3</v>
+        <v>22.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>24</v>
+        <v>46.2</v>
       </c>
       <c r="R22" t="n">
-        <v>54.9</v>
+        <v>40.1</v>
       </c>
       <c r="S22" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U22" t="n">
-        <v>13</v>
+        <v>40.3</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -6455,7 +6431,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -6476,7 +6452,7 @@
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr"/>
@@ -6493,12 +6469,12 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -6508,127 +6484,127 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 0 HR</t>
+          <t>Contact streak: 7/18 over last 7 games</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>100.1411</t>
+          <t>98.8542</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.4642</t>
+          <t>0.316</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>0.1811</t>
+          <t>0.129</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.227</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>0.1615</t>
+          <t>0.206</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>0.1122</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>25.43</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr"/>
@@ -6639,56 +6615,56 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>806956</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ethan Salas</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>45.9</v>
+        <v>45.7</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6702,26 +6678,26 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>22.6</v>
+        <v>39.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>46.2</v>
+        <v>24</v>
       </c>
       <c r="R23" t="n">
-        <v>40.1</v>
+        <v>51.9</v>
       </c>
       <c r="S23" t="n">
-        <v>86.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="T23" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U23" t="n">
-        <v>40.3</v>
+        <v>13</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -6735,7 +6711,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -6756,7 +6732,7 @@
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr"/>
@@ -6773,12 +6749,12 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -6788,127 +6764,127 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Contact streak: 7/18 over last 7 games</t>
+          <t>Last 7 games: 6/29, 0 HR</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>98.8542</t>
+          <t>100.1411</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>0.4642</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>0.1811</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>0.3591</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>0.1615</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>0.4132</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1122</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>25.43</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr"/>
@@ -6944,7 +6920,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -6968,7 +6944,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>45.3</v>
+        <v>44.9</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -6992,7 +6968,7 @@
         <v>24</v>
       </c>
       <c r="R24" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S24" t="n">
         <v>64.3</v>
@@ -7183,7 +7159,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -7504,7 +7480,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -7528,7 +7504,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>39.5</v>
+        <v>39</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7552,7 +7528,7 @@
         <v>24</v>
       </c>
       <c r="R26" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S26" t="n">
         <v>44.8</v>
@@ -7743,7 +7719,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -7784,7 +7760,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -7808,7 +7784,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>39.2</v>
+        <v>38.8</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -7832,7 +7808,7 @@
         <v>24.6</v>
       </c>
       <c r="R27" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S27" t="n">
         <v>94.90000000000001</v>
@@ -8023,7 +7999,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -8344,7 +8320,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -8368,7 +8344,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>38.1</v>
+        <v>37.6</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -8392,7 +8368,7 @@
         <v>24</v>
       </c>
       <c r="R29" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S29" t="n">
         <v>76.2</v>
@@ -8583,7 +8559,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -8624,7 +8600,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -8648,7 +8624,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>37.6</v>
+        <v>37.2</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -8672,7 +8648,7 @@
         <v>24</v>
       </c>
       <c r="R30" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S30" t="n">
         <v>52.4</v>
@@ -8863,7 +8839,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -8879,47 +8855,47 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>657041</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Lane Thomas</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>601713</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -8928,7 +8904,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>36.6</v>
+        <v>35.8</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -8942,65 +8918,61 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>16.6</v>
+        <v>24.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>47.3</v>
+        <v>26.6</v>
       </c>
       <c r="R31" t="n">
-        <v>40.1</v>
+        <v>51.9</v>
       </c>
       <c r="S31" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T31" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U31" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr"/>
@@ -9017,12 +8989,12 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -9032,127 +9004,127 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 1/16, 0 HR</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>38.02</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.85</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>99.4812</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3371</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.1201</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.2906</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>72.63</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>24.73</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>42.12</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.1449</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>40.24</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>0.3834</t>
+          <t>0.3257</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>22.66</t>
         </is>
       </c>
       <c r="BG31" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr"/>
@@ -9163,27 +9135,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>657041</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lane Thomas</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9198,12 +9170,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>601713</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -9212,7 +9184,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>36.3</v>
+        <v>35.8</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -9230,13 +9202,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>24.7</v>
+        <v>10.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>26.6</v>
+        <v>48.2</v>
       </c>
       <c r="R32" t="n">
-        <v>54.9</v>
+        <v>40.1</v>
       </c>
       <c r="S32" t="n">
         <v>64.3</v>
@@ -9245,7 +9217,7 @@
         <v>50</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>24.9</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -9280,7 +9252,7 @@
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr"/>
@@ -9297,12 +9269,12 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -9312,127 +9284,127 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/16, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>38.02</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>88.85</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>99.4812</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>0.3371</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>0.1201</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>0.2906</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>72.63</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>24.73</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>42.12</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>0.1449</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>40.24</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.3834</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="BG32" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr"/>
@@ -9468,7 +9440,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -9492,7 +9464,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>35.7</v>
+        <v>35.2</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -9516,7 +9488,7 @@
         <v>26.6</v>
       </c>
       <c r="R33" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S33" t="n">
         <v>76.2</v>
@@ -9707,7 +9679,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -9723,12 +9695,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>687401</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Joey Ortiz</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -9753,7 +9725,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -9786,11 +9758,11 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>10.5</v>
+        <v>17.1</v>
       </c>
       <c r="Q34" t="n">
         <v>48.2</v>
@@ -9799,52 +9771,48 @@
         <v>40.1</v>
       </c>
       <c r="S34" t="n">
-        <v>59.8</v>
+        <v>44.8</v>
       </c>
       <c r="T34" t="n">
         <v>50</v>
       </c>
       <c r="U34" t="n">
-        <v>24.9</v>
+        <v>22.4</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr"/>
@@ -9861,12 +9829,12 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -9876,7 +9844,7 @@
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
@@ -9891,67 +9859,67 @@
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>36.16</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.91</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>99.2209</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3403</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2904</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>31.91</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.1185</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
@@ -10007,12 +9975,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -10037,7 +10005,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -10056,7 +10024,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>34.5</v>
+        <v>34.7</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -10070,11 +10038,11 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>17.1</v>
+        <v>5.4</v>
       </c>
       <c r="Q35" t="n">
         <v>48.2</v>
@@ -10083,49 +10051,45 @@
         <v>40.1</v>
       </c>
       <c r="S35" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T35" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U35" t="n">
-        <v>22.4</v>
+        <v>17.3</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10145,12 +10109,12 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -10160,12 +10124,12 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
@@ -10175,67 +10139,67 @@
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>87.91</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>99.2209</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.2904</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.1185</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
@@ -10596,7 +10560,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -10620,7 +10584,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>29</v>
+        <v>28.5</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -10644,7 +10608,7 @@
         <v>26.6</v>
       </c>
       <c r="R37" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S37" t="n">
         <v>44.8</v>
@@ -10835,7 +10799,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI37" t="inlineStr">
@@ -11207,7 +11171,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -11226,7 +11190,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>58.2</v>
+        <v>59.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -11240,7 +11204,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -11253,7 +11217,7 @@
         <v>40.1</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -11263,39 +11227,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11486,7 +11446,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -11510,7 +11470,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>58.1</v>
+        <v>57.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -11534,7 +11494,7 @@
         <v>26.6</v>
       </c>
       <c r="R3" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S3" t="n">
         <v>96.59999999999999</v>
@@ -11725,7 +11685,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -12021,27 +11981,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>660271</t>
+          <t>701538</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Shohei Ohtani</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -12051,26 +12011,26 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>57.2</v>
+        <v>57</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -12084,26 +12044,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>79.3</v>
+        <v>54.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>24</v>
+        <v>46.2</v>
       </c>
       <c r="R5" t="n">
-        <v>54.9</v>
+        <v>40.1</v>
       </c>
       <c r="S5" t="n">
-        <v>86.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>8.800000000000001</v>
+        <v>16.6</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -12117,7 +12077,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -12155,12 +12115,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -12170,127 +12130,127 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/28, 0 HR</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>54.08</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>93.78</t>
+          <t>90.96</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>104.473</t>
+          <t>101.2045</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.5811</t>
+          <t>0.4907</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.2987</t>
+          <t>0.2228</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4054</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>75.03</t>
+          <t>72.95</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>52.94</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>31.92</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.2679</t>
+          <t>0.1881</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.1122</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>25.43</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr"/>
@@ -12301,56 +12261,56 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>701538</t>
+          <t>660271</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Shohei Ohtani</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>57</v>
+        <v>56.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -12364,26 +12324,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>54.2</v>
+        <v>79.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>46.2</v>
+        <v>24</v>
       </c>
       <c r="R6" t="n">
-        <v>40.1</v>
+        <v>51.9</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>16.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -12397,7 +12357,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -12435,12 +12395,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -12450,127 +12410,127 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 5/28, 0 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>18.53</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>54.08</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>90.96</t>
+          <t>93.78</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>101.2045</t>
+          <t>104.473</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4907</t>
+          <t>0.5811</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.2228</t>
+          <t>0.2987</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.4054</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>72.95</t>
+          <t>75.03</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>31.92</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1881</t>
+          <t>0.2679</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.4132</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1122</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>25.43</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr"/>
@@ -12606,7 +12566,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -12630,7 +12590,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>56.3</v>
+        <v>55.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -12654,7 +12614,7 @@
         <v>26.6</v>
       </c>
       <c r="R7" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S7" t="n">
         <v>93.2</v>
@@ -12845,7 +12805,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -12886,7 +12846,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -12910,7 +12870,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>56.2</v>
+        <v>55.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -12934,7 +12894,7 @@
         <v>24</v>
       </c>
       <c r="R8" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S8" t="n">
         <v>94.90000000000001</v>
@@ -13125,7 +13085,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -13141,27 +13101,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>660670</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ronald Acuña Jr.</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -13171,17 +13131,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>601713</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -13190,7 +13150,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>55.2</v>
+        <v>54.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -13208,22 +13168,22 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>58.7</v>
+        <v>50.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>26.6</v>
+        <v>48.2</v>
       </c>
       <c r="R9" t="n">
-        <v>54.9</v>
+        <v>40.1</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>53.3</v>
+        <v>63.3</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -13237,7 +13197,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -13275,142 +13235,142 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.53</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>102.9585</t>
+          <t>101.9338</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.507</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.2461</t>
+          <t>0.2007</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3753</t>
+          <t>0.3329</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>75.91</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>61.27</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>36.58</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.2056</t>
+          <t>0.1951</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>40.24</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.3834</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr"/>
@@ -13421,47 +13381,47 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>660670</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Ronald Acuña Jr.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>601713</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -13470,7 +13430,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>54.2</v>
+        <v>54.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -13484,62 +13444,58 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>50.1</v>
+        <v>58.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>48.2</v>
+        <v>26.6</v>
       </c>
       <c r="R10" t="n">
-        <v>40.1</v>
+        <v>51.9</v>
       </c>
       <c r="S10" t="n">
-        <v>88.7</v>
+        <v>100</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>63.3</v>
+        <v>53.3</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -13559,142 +13515,142 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>13.81</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>90.53</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.9338</t>
+          <t>102.9585</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.507</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.2461</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.3753</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>75.91</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>61.27</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>36.58</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1951</t>
+          <t>0.2056</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>40.24</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.3834</t>
+          <t>0.3257</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>22.66</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr"/>
@@ -13735,7 +13691,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -13754,7 +13710,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>53.5</v>
+        <v>53.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -13768,7 +13724,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -13781,7 +13737,7 @@
         <v>40.1</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
@@ -13791,39 +13747,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14269,56 +14221,56 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>601713</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>52.4</v>
+        <v>51.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -14332,62 +14284,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>47.1</v>
+        <v>45.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>48.2</v>
+        <v>24</v>
       </c>
       <c r="R13" t="n">
-        <v>40.1</v>
+        <v>51.9</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>13.3</v>
+        <v>48.3</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14407,142 +14355,142 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>EV profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>101.5782</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4427</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1878</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>40.24</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.3834</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.1122</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr"/>
@@ -14553,27 +14501,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Teoscar Hernández</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -14583,26 +14531,26 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>601713</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>52</v>
+        <v>51.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -14616,26 +14564,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>45.7</v>
+        <v>47.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>24</v>
+        <v>48.2</v>
       </c>
       <c r="R14" t="n">
-        <v>54.9</v>
+        <v>40.1</v>
       </c>
       <c r="S14" t="n">
-        <v>96.59999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>48.3</v>
+        <v>13.3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -14649,7 +14597,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -14687,142 +14635,142 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>101.5782</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1878</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>77.51</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>40.24</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.3834</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1122</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr"/>
@@ -14833,27 +14781,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>671739</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Michael Harris II</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -14868,12 +14816,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>601713</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -14882,7 +14830,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>50.4</v>
+        <v>50.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -14900,13 +14848,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>45.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>26.6</v>
+        <v>48.2</v>
       </c>
       <c r="R15" t="n">
-        <v>54.9</v>
+        <v>40.1</v>
       </c>
       <c r="S15" t="n">
         <v>86.40000000000001</v>
@@ -14915,7 +14863,7 @@
         <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>32</v>
+        <v>25.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -14967,142 +14915,142 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>46.34</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>90.41</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>103.0958</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.4653</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1816</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3339</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>74.72</t>
+          <t>73.16</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1859</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>40.24</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.3834</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr"/>
@@ -15143,7 +15091,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -15162,7 +15110,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>49.7</v>
+        <v>50.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -15176,7 +15124,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -15189,7 +15137,7 @@
         <v>40.1</v>
       </c>
       <c r="S16" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T16" t="n">
         <v>50</v>
@@ -15199,39 +15147,35 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -15397,47 +15341,47 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>671739</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>601713</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -15446,7 +15390,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>48.7</v>
+        <v>49.9</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -15460,62 +15404,58 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>38.2</v>
+        <v>45.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>48.2</v>
+        <v>26.6</v>
       </c>
       <c r="R17" t="n">
-        <v>40.1</v>
+        <v>51.9</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>25.3</v>
+        <v>32</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -15535,142 +15475,142 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>46.34</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.41</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>103.0958</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4653</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1816</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3339</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>73.16</t>
+          <t>74.72</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1859</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>40.24</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.3834</t>
+          <t>0.3257</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>22.66</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr"/>
@@ -16266,7 +16206,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -16290,7 +16230,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>46.5</v>
+        <v>46</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -16314,7 +16254,7 @@
         <v>26.6</v>
       </c>
       <c r="R20" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S20" t="n">
         <v>52.4</v>
@@ -16505,7 +16445,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -16546,7 +16486,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -16570,7 +16510,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>46.3</v>
+        <v>45.9</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -16594,7 +16534,7 @@
         <v>24</v>
       </c>
       <c r="R21" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S21" t="n">
         <v>93.2</v>
@@ -16785,7 +16725,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
